--- a/5. SMS Reports/.Reports/12. Dec/SMS-Cary 12.31.25 Financial Report_Final.xlsx
+++ b/5. SMS Reports/.Reports/12. Dec/SMS-Cary 12.31.25 Financial Report_Final.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General Ledger" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Month Statement" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Month Statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mm-yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm-yyyy"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -195,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -227,7 +226,7 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -392,6 +391,9 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -904,7 +906,7 @@
       <c r="C8" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -947,7 +949,7 @@
       <c r="C9" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -990,7 +992,7 @@
       <c r="C10" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1037,7 +1039,7 @@
       <c r="C11" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1080,7 +1082,7 @@
       <c r="C12" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1127,7 +1129,7 @@
       <c r="C13" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1174,7 +1176,7 @@
       <c r="C14" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1221,7 +1223,7 @@
       <c r="C15" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1264,7 +1266,7 @@
       <c r="C16" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1311,7 +1313,7 @@
       <c r="C17" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1358,7 +1360,7 @@
       <c r="C18" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1401,7 +1403,7 @@
       <c r="C19" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1444,7 +1446,7 @@
       <c r="C20" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1487,7 +1489,7 @@
       <c r="C21" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1534,7 +1536,7 @@
       <c r="C22" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1581,7 +1583,7 @@
       <c r="C23" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1624,7 +1626,7 @@
       <c r="C24" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1667,7 +1669,7 @@
       <c r="C25" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1710,7 +1712,7 @@
       <c r="C26" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1753,7 +1755,7 @@
       <c r="C27" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1800,7 +1802,7 @@
       <c r="C28" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1847,7 +1849,7 @@
       <c r="C29" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1894,7 +1896,7 @@
       <c r="C30" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1941,7 +1943,7 @@
       <c r="C31" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1988,7 +1990,7 @@
       <c r="C32" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2035,7 +2037,7 @@
       <c r="C33" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2082,7 +2084,7 @@
       <c r="C34" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2129,7 +2131,7 @@
       <c r="C35" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2176,7 +2178,7 @@
       <c r="C36" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2223,7 +2225,7 @@
       <c r="C37" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2270,7 +2272,7 @@
       <c r="C38" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2317,7 +2319,7 @@
       <c r="C39" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2364,7 +2366,7 @@
       <c r="C40" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2411,7 +2413,7 @@
       <c r="C41" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2458,7 +2460,7 @@
       <c r="C42" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2505,7 +2507,7 @@
       <c r="C43" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2552,7 +2554,7 @@
       <c r="C44" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D44" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2595,7 +2597,7 @@
       <c r="C45" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2638,7 +2640,7 @@
       <c r="C46" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -2681,7 +2683,7 @@
       <c r="C47" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2724,7 +2726,7 @@
       <c r="C48" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2767,7 +2769,7 @@
       <c r="C49" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2814,7 +2816,7 @@
       <c r="C50" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2857,7 +2859,7 @@
       <c r="C51" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2904,7 +2906,7 @@
       <c r="C52" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D52" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -2951,7 +2953,7 @@
       <c r="C53" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D53" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -2994,7 +2996,7 @@
       <c r="C54" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D54" s="11" t="n">
+      <c r="D54" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -3037,7 +3039,7 @@
       <c r="C55" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D55" s="11" t="n">
+      <c r="D55" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -3080,7 +3082,7 @@
       <c r="C56" s="10" t="n">
         <v>46017</v>
       </c>
-      <c r="D56" s="11" t="n">
+      <c r="D56" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3123,7 +3125,7 @@
       <c r="C57" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D57" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3166,7 +3168,7 @@
       <c r="C58" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D58" s="11" t="n">
+      <c r="D58" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -3209,7 +3211,7 @@
       <c r="C59" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D59" s="11" t="n">
+      <c r="D59" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -3252,7 +3254,7 @@
       <c r="C60" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D60" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -3295,7 +3297,7 @@
       <c r="C61" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D61" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3338,7 +3340,7 @@
       <c r="C62" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D62" s="11" t="n">
+      <c r="D62" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3381,7 +3383,7 @@
       <c r="C63" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D63" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3428,7 +3430,7 @@
       <c r="C64" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D64" s="11" t="n">
+      <c r="D64" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E64" s="9" t="inlineStr">
@@ -3546,7 +3548,7 @@
       <c r="C68" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D68" s="11" t="n">
+      <c r="D68" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3589,7 +3591,7 @@
       <c r="C69" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D69" s="11" t="n">
+      <c r="D69" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3632,7 +3634,7 @@
       <c r="C70" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D70" s="11" t="n">
+      <c r="D70" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -3675,7 +3677,7 @@
       <c r="C71" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D71" s="11" t="n">
+      <c r="D71" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -3718,7 +3720,7 @@
       <c r="C72" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D72" s="11" t="n">
+      <c r="D72" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3761,7 +3763,7 @@
       <c r="C73" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D73" s="11" t="n">
+      <c r="D73" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -3804,7 +3806,7 @@
       <c r="C74" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D74" s="11" t="n">
+      <c r="D74" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3847,7 +3849,7 @@
       <c r="C75" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D75" s="11" t="n">
+      <c r="D75" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -3890,7 +3892,7 @@
       <c r="C76" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D76" s="11" t="n">
+      <c r="D76" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3933,7 +3935,7 @@
       <c r="C77" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D77" s="11" t="n">
+      <c r="D77" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -3976,7 +3978,7 @@
       <c r="C78" s="10" t="n">
         <v>46017</v>
       </c>
-      <c r="D78" s="11" t="n">
+      <c r="D78" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4019,7 +4021,7 @@
       <c r="C79" s="10" t="n">
         <v>46017</v>
       </c>
-      <c r="D79" s="11" t="n">
+      <c r="D79" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4062,7 +4064,7 @@
       <c r="C80" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D80" s="11" t="n">
+      <c r="D80" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -4105,7 +4107,7 @@
       <c r="C81" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D81" s="11" t="n">
+      <c r="D81" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -4148,7 +4150,7 @@
       <c r="C82" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D82" s="11" t="n">
+      <c r="D82" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E82" s="9" t="inlineStr">
@@ -4262,7 +4264,7 @@
       <c r="C86" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D86" s="11" t="n">
+      <c r="D86" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E86" s="9" t="inlineStr">
@@ -4735,7 +4737,7 @@
       <c r="C105" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D105" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -4849,7 +4851,7 @@
       <c r="C109" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D109" s="11" t="n">
+      <c r="D109" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -4892,7 +4894,7 @@
       <c r="C110" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D110" s="11" t="n">
+      <c r="D110" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -5077,7 +5079,7 @@
       <c r="C117" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D117" s="11" t="n">
+      <c r="D117" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -5124,7 +5126,7 @@
       <c r="C118" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D118" s="11" t="n">
+      <c r="D118" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -5171,7 +5173,7 @@
       <c r="C119" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D119" s="11" t="n">
+      <c r="D119" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -5218,7 +5220,7 @@
       <c r="C120" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D120" s="11" t="n">
+      <c r="D120" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -5265,7 +5267,7 @@
       <c r="C121" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D121" s="11" t="n">
+      <c r="D121" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E121" s="9" t="inlineStr">
@@ -5312,7 +5314,7 @@
       <c r="C122" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D122" s="11" t="n">
+      <c r="D122" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E122" s="9" t="inlineStr">
@@ -5359,7 +5361,7 @@
       <c r="C123" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D123" s="11" t="n">
+      <c r="D123" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E123" s="9" t="inlineStr">
@@ -5406,7 +5408,7 @@
       <c r="C124" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D124" s="11" t="n">
+      <c r="D124" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E124" s="9" t="inlineStr">
@@ -5453,7 +5455,7 @@
       <c r="C125" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D125" s="11" t="n">
+      <c r="D125" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E125" s="9" t="inlineStr">
@@ -5500,7 +5502,7 @@
       <c r="C126" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D126" s="11" t="n">
+      <c r="D126" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E126" s="9" t="inlineStr">
@@ -5547,7 +5549,7 @@
       <c r="C127" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D127" s="11" t="n">
+      <c r="D127" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E127" s="9" t="inlineStr">
@@ -5594,7 +5596,7 @@
       <c r="C128" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D128" s="11" t="n">
+      <c r="D128" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E128" s="9" t="inlineStr">
@@ -5641,7 +5643,7 @@
       <c r="C129" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D129" s="11" t="n">
+      <c r="D129" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E129" s="9" t="inlineStr">
@@ -5688,7 +5690,7 @@
       <c r="C130" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D130" s="11" t="n">
+      <c r="D130" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E130" s="9" t="inlineStr">
@@ -5735,7 +5737,7 @@
       <c r="C131" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D131" s="11" t="n">
+      <c r="D131" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -5782,7 +5784,7 @@
       <c r="C132" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D132" s="11" t="n">
+      <c r="D132" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E132" s="9" t="inlineStr">
@@ -5829,7 +5831,7 @@
       <c r="C133" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D133" s="11" t="n">
+      <c r="D133" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -5876,7 +5878,7 @@
       <c r="C134" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D134" s="11" t="n">
+      <c r="D134" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -5923,7 +5925,7 @@
       <c r="C135" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D135" s="11" t="n">
+      <c r="D135" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -5970,7 +5972,7 @@
       <c r="C136" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D136" s="11" t="n">
+      <c r="D136" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E136" s="9" t="inlineStr">
@@ -6017,7 +6019,7 @@
       <c r="C137" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D137" s="11" t="n">
+      <c r="D137" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E137" s="9" t="inlineStr">
@@ -6064,7 +6066,7 @@
       <c r="C138" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D138" s="11" t="n">
+      <c r="D138" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -6111,7 +6113,7 @@
       <c r="C139" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D139" s="11" t="n">
+      <c r="D139" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E139" s="9" t="inlineStr">
@@ -6158,7 +6160,7 @@
       <c r="C140" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D140" s="11" t="n">
+      <c r="D140" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -6205,7 +6207,7 @@
       <c r="C141" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D141" s="11" t="n">
+      <c r="D141" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -6252,7 +6254,7 @@
       <c r="C142" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D142" s="11" t="n">
+      <c r="D142" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E142" s="9" t="inlineStr">
@@ -6299,7 +6301,7 @@
       <c r="C143" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D143" s="11" t="n">
+      <c r="D143" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E143" s="9" t="inlineStr">
@@ -6346,7 +6348,7 @@
       <c r="C144" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D144" s="11" t="n">
+      <c r="D144" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E144" s="9" t="inlineStr">
@@ -6393,7 +6395,7 @@
       <c r="C145" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D145" s="11" t="n">
+      <c r="D145" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -6440,7 +6442,7 @@
       <c r="C146" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D146" s="11" t="n">
+      <c r="D146" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E146" s="9" t="inlineStr">
@@ -6487,7 +6489,7 @@
       <c r="C147" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D147" s="11" t="n">
+      <c r="D147" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -6534,7 +6536,7 @@
       <c r="C148" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D148" s="11" t="n">
+      <c r="D148" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E148" s="9" t="inlineStr">
@@ -6581,7 +6583,7 @@
       <c r="C149" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D149" s="11" t="n">
+      <c r="D149" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E149" s="9" t="inlineStr">
@@ -6628,7 +6630,7 @@
       <c r="C150" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D150" s="11" t="n">
+      <c r="D150" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E150" s="9" t="inlineStr">
@@ -6675,7 +6677,7 @@
       <c r="C151" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D151" s="11" t="n">
+      <c r="D151" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E151" s="9" t="inlineStr">
@@ -6722,7 +6724,7 @@
       <c r="C152" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D152" s="11" t="n">
+      <c r="D152" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E152" s="9" t="inlineStr">
@@ -6769,7 +6771,7 @@
       <c r="C153" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D153" s="11" t="n">
+      <c r="D153" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E153" s="9" t="inlineStr">
@@ -6816,7 +6818,7 @@
       <c r="C154" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D154" s="11" t="n">
+      <c r="D154" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E154" s="9" t="inlineStr">
@@ -6863,7 +6865,7 @@
       <c r="C155" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D155" s="11" t="n">
+      <c r="D155" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E155" s="9" t="inlineStr">
@@ -6910,7 +6912,7 @@
       <c r="C156" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D156" s="11" t="n">
+      <c r="D156" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E156" s="9" t="inlineStr">
@@ -6957,7 +6959,7 @@
       <c r="C157" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D157" s="11" t="n">
+      <c r="D157" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E157" s="9" t="inlineStr">
@@ -7004,7 +7006,7 @@
       <c r="C158" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D158" s="11" t="n">
+      <c r="D158" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E158" s="9" t="inlineStr">
@@ -7051,7 +7053,7 @@
       <c r="C159" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D159" s="11" t="n">
+      <c r="D159" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E159" s="9" t="inlineStr">
@@ -7098,7 +7100,7 @@
       <c r="C160" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D160" s="11" t="n">
+      <c r="D160" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E160" s="9" t="inlineStr">
@@ -7145,7 +7147,7 @@
       <c r="C161" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D161" s="11" t="n">
+      <c r="D161" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E161" s="9" t="inlineStr">
@@ -7192,7 +7194,7 @@
       <c r="C162" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D162" s="11" t="n">
+      <c r="D162" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E162" s="9" t="inlineStr">
@@ -7239,7 +7241,7 @@
       <c r="C163" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D163" s="11" t="n">
+      <c r="D163" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E163" s="9" t="inlineStr">
@@ -7286,7 +7288,7 @@
       <c r="C164" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D164" s="11" t="n">
+      <c r="D164" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E164" s="9" t="inlineStr">
@@ -7333,7 +7335,7 @@
       <c r="C165" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D165" s="11" t="n">
+      <c r="D165" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E165" s="9" t="inlineStr">
@@ -7380,7 +7382,7 @@
       <c r="C166" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D166" s="11" t="n">
+      <c r="D166" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E166" s="9" t="inlineStr">
@@ -7427,7 +7429,7 @@
       <c r="C167" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D167" s="11" t="n">
+      <c r="D167" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E167" s="9" t="inlineStr">
@@ -7474,7 +7476,7 @@
       <c r="C168" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D168" s="11" t="n">
+      <c r="D168" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E168" s="9" t="inlineStr">
@@ -7521,7 +7523,7 @@
       <c r="C169" s="10" t="n">
         <v>46023</v>
       </c>
-      <c r="D169" s="11" t="n">
+      <c r="D169" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E169" s="9" t="inlineStr">
@@ -7568,7 +7570,7 @@
       <c r="C170" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D170" s="11" t="n">
+      <c r="D170" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E170" s="9" t="inlineStr">
@@ -7615,7 +7617,7 @@
       <c r="C171" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D171" s="11" t="n">
+      <c r="D171" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E171" s="9" t="inlineStr">
@@ -7662,7 +7664,7 @@
       <c r="C172" s="10" t="n">
         <v>46026</v>
       </c>
-      <c r="D172" s="11" t="n">
+      <c r="D172" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E172" s="9" t="inlineStr">
@@ -7709,7 +7711,7 @@
       <c r="C173" s="10" t="n">
         <v>46031</v>
       </c>
-      <c r="D173" s="11" t="n">
+      <c r="D173" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E173" s="9" t="inlineStr">
@@ -7827,7 +7829,7 @@
       <c r="C177" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D177" s="11" t="n">
+      <c r="D177" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E177" s="9" t="inlineStr">
@@ -7870,7 +7872,7 @@
       <c r="C178" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D178" s="11" t="n">
+      <c r="D178" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E178" s="9" t="inlineStr">
@@ -7913,7 +7915,7 @@
       <c r="C179" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D179" s="11" t="n">
+      <c r="D179" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E179" s="9" t="inlineStr">
@@ -7956,7 +7958,7 @@
       <c r="C180" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D180" s="11" t="n">
+      <c r="D180" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E180" s="9" t="inlineStr">
@@ -7999,7 +8001,7 @@
       <c r="C181" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D181" s="11" t="n">
+      <c r="D181" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E181" s="9" t="inlineStr">
@@ -8042,7 +8044,7 @@
       <c r="C182" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D182" s="11" t="n">
+      <c r="D182" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E182" s="9" t="inlineStr">
@@ -8085,7 +8087,7 @@
       <c r="C183" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D183" s="11" t="n">
+      <c r="D183" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E183" s="9" t="inlineStr">
@@ -8128,7 +8130,7 @@
       <c r="C184" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D184" s="11" t="n">
+      <c r="D184" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E184" s="9" t="inlineStr">
@@ -8171,7 +8173,7 @@
       <c r="C185" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D185" s="11" t="n">
+      <c r="D185" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E185" s="9" t="inlineStr">
@@ -8214,7 +8216,7 @@
       <c r="C186" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D186" s="11" t="n">
+      <c r="D186" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E186" s="9" t="inlineStr">
@@ -8257,7 +8259,7 @@
       <c r="C187" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D187" s="11" t="n">
+      <c r="D187" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E187" s="9" t="inlineStr">
@@ -8300,7 +8302,7 @@
       <c r="C188" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D188" s="11" t="n">
+      <c r="D188" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E188" s="9" t="inlineStr">
@@ -8556,7 +8558,7 @@
       <c r="C198" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D198" s="11" t="n">
+      <c r="D198" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E198" s="9" t="inlineStr">
@@ -8674,7 +8676,7 @@
       <c r="C202" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D202" s="11" t="n">
+      <c r="D202" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E202" s="9" t="inlineStr">
@@ -8717,7 +8719,7 @@
       <c r="C203" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D203" s="11" t="n">
+      <c r="D203" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E203" s="9" t="inlineStr">
@@ -8760,7 +8762,7 @@
       <c r="C204" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D204" s="11" t="n">
+      <c r="D204" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E204" s="9" t="inlineStr">
@@ -8803,7 +8805,7 @@
       <c r="C205" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D205" s="11" t="n">
+      <c r="D205" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E205" s="9" t="inlineStr">
@@ -8846,7 +8848,7 @@
       <c r="C206" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D206" s="11" t="n">
+      <c r="D206" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E206" s="9" t="inlineStr">
@@ -8889,7 +8891,7 @@
       <c r="C207" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D207" s="11" t="n">
+      <c r="D207" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E207" s="9" t="inlineStr">
@@ -9003,7 +9005,7 @@
       <c r="C211" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D211" s="11" t="n">
+      <c r="D211" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E211" s="9" t="inlineStr">
@@ -9046,7 +9048,7 @@
       <c r="C212" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D212" s="11" t="n">
+      <c r="D212" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E212" s="9" t="inlineStr">
@@ -9093,7 +9095,7 @@
       <c r="C213" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D213" s="11" t="n">
+      <c r="D213" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E213" s="9" t="inlineStr">
@@ -9136,7 +9138,7 @@
       <c r="C214" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D214" s="11" t="n">
+      <c r="D214" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E214" s="9" t="inlineStr">
@@ -9183,7 +9185,7 @@
       <c r="C215" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D215" s="11" t="n">
+      <c r="D215" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E215" s="9" t="inlineStr">
@@ -9226,7 +9228,7 @@
       <c r="C216" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D216" s="11" t="n">
+      <c r="D216" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E216" s="9" t="inlineStr">
@@ -9269,7 +9271,7 @@
       <c r="C217" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D217" s="11" t="n">
+      <c r="D217" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E217" s="9" t="inlineStr">
@@ -9312,7 +9314,7 @@
       <c r="C218" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D218" s="11" t="n">
+      <c r="D218" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E218" s="9" t="inlineStr">
@@ -9426,7 +9428,7 @@
       <c r="C222" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D222" s="11" t="n">
+      <c r="D222" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E222" s="9" t="inlineStr">
@@ -9753,7 +9755,7 @@
       <c r="C235" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D235" s="11" t="n">
+      <c r="D235" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E235" s="9" t="inlineStr">
@@ -9796,7 +9798,7 @@
       <c r="C236" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D236" s="11" t="n">
+      <c r="D236" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E236" s="9" t="inlineStr">
@@ -9839,7 +9841,7 @@
       <c r="C237" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D237" s="11" t="n">
+      <c r="D237" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E237" s="9" t="inlineStr">
@@ -9882,7 +9884,7 @@
       <c r="C238" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D238" s="11" t="n">
+      <c r="D238" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E238" s="9" t="inlineStr">
@@ -9925,7 +9927,7 @@
       <c r="C239" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D239" s="11" t="n">
+      <c r="D239" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E239" s="9" t="inlineStr">
@@ -9968,7 +9970,7 @@
       <c r="C240" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D240" s="11" t="n">
+      <c r="D240" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E240" s="9" t="inlineStr">
@@ -10011,7 +10013,7 @@
       <c r="C241" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D241" s="11" t="n">
+      <c r="D241" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E241" s="9" t="inlineStr">
@@ -10054,7 +10056,7 @@
       <c r="C242" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D242" s="11" t="n">
+      <c r="D242" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E242" s="9" t="inlineStr">
@@ -10097,7 +10099,7 @@
       <c r="C243" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D243" s="11" t="n">
+      <c r="D243" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E243" s="9" t="inlineStr">
@@ -10140,7 +10142,7 @@
       <c r="C244" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D244" s="11" t="n">
+      <c r="D244" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E244" s="9" t="inlineStr">
@@ -10183,7 +10185,7 @@
       <c r="C245" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D245" s="11" t="n">
+      <c r="D245" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E245" s="9" t="inlineStr">
@@ -10226,7 +10228,7 @@
       <c r="C246" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D246" s="11" t="n">
+      <c r="D246" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E246" s="9" t="inlineStr">
@@ -10269,7 +10271,7 @@
       <c r="C247" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D247" s="11" t="n">
+      <c r="D247" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E247" s="9" t="inlineStr">
@@ -10312,7 +10314,7 @@
       <c r="C248" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D248" s="11" t="n">
+      <c r="D248" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E248" s="9" t="inlineStr">
@@ -10355,7 +10357,7 @@
       <c r="C249" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D249" s="11" t="n">
+      <c r="D249" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E249" s="9" t="inlineStr">
@@ -10398,7 +10400,7 @@
       <c r="C250" s="10" t="n">
         <v>46015</v>
       </c>
-      <c r="D250" s="11" t="n">
+      <c r="D250" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E250" s="9" t="inlineStr">
@@ -10441,7 +10443,7 @@
       <c r="C251" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D251" s="11" t="n">
+      <c r="D251" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E251" s="9" t="inlineStr">
@@ -10484,7 +10486,7 @@
       <c r="C252" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D252" s="11" t="n">
+      <c r="D252" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E252" s="9" t="inlineStr">
@@ -10527,7 +10529,7 @@
       <c r="C253" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D253" s="11" t="n">
+      <c r="D253" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E253" s="9" t="inlineStr">
@@ -10570,7 +10572,7 @@
       <c r="C254" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D254" s="11" t="n">
+      <c r="D254" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E254" s="9" t="inlineStr">
@@ -10613,7 +10615,7 @@
       <c r="C255" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D255" s="11" t="n">
+      <c r="D255" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E255" s="9" t="inlineStr">
@@ -10656,7 +10658,7 @@
       <c r="C256" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D256" s="11" t="n">
+      <c r="D256" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E256" s="9" t="inlineStr">
@@ -10699,7 +10701,7 @@
       <c r="C257" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D257" s="11" t="n">
+      <c r="D257" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E257" s="9" t="inlineStr">
@@ -10742,7 +10744,7 @@
       <c r="C258" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D258" s="11" t="n">
+      <c r="D258" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E258" s="9" t="inlineStr">
@@ -10785,7 +10787,7 @@
       <c r="C259" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D259" s="11" t="n">
+      <c r="D259" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E259" s="9" t="inlineStr">
@@ -10828,7 +10830,7 @@
       <c r="C260" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D260" s="11" t="n">
+      <c r="D260" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E260" s="9" t="inlineStr">
@@ -10871,7 +10873,7 @@
       <c r="C261" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D261" s="11" t="n">
+      <c r="D261" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E261" s="9" t="inlineStr">
@@ -10985,7 +10987,7 @@
       <c r="C265" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D265" s="11" t="n">
+      <c r="D265" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E265" s="9" t="inlineStr">
@@ -11099,7 +11101,7 @@
       <c r="C269" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D269" s="11" t="n">
+      <c r="D269" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E269" s="9" t="inlineStr">
@@ -11213,7 +11215,7 @@
       <c r="C273" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D273" s="11" t="n">
+      <c r="D273" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E273" s="9" t="inlineStr">
@@ -11256,7 +11258,7 @@
       <c r="C274" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D274" s="11" t="n">
+      <c r="D274" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E274" s="9" t="inlineStr">
@@ -11299,7 +11301,7 @@
       <c r="C275" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D275" s="11" t="n">
+      <c r="D275" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E275" s="9" t="inlineStr">
@@ -11342,7 +11344,7 @@
       <c r="C276" s="10" t="n">
         <v>46017</v>
       </c>
-      <c r="D276" s="11" t="n">
+      <c r="D276" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E276" s="9" t="inlineStr">
@@ -11456,7 +11458,7 @@
       <c r="C280" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D280" s="11" t="n">
+      <c r="D280" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E280" s="9" t="inlineStr">
@@ -11570,7 +11572,7 @@
       <c r="C284" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D284" s="11" t="n">
+      <c r="D284" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E284" s="9" t="inlineStr">
@@ -11684,7 +11686,7 @@
       <c r="C288" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D288" s="11" t="n">
+      <c r="D288" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E288" s="9" t="inlineStr">
@@ -11727,7 +11729,7 @@
       <c r="C289" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D289" s="11" t="n">
+      <c r="D289" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E289" s="9" t="inlineStr">
@@ -11770,7 +11772,7 @@
       <c r="C290" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D290" s="11" t="n">
+      <c r="D290" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E290" s="9" t="inlineStr">
@@ -11813,7 +11815,7 @@
       <c r="C291" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D291" s="11" t="n">
+      <c r="D291" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E291" s="9" t="inlineStr">
@@ -11856,7 +11858,7 @@
       <c r="C292" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D292" s="11" t="n">
+      <c r="D292" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E292" s="9" t="inlineStr">
@@ -11899,7 +11901,7 @@
       <c r="C293" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D293" s="11" t="n">
+      <c r="D293" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E293" s="9" t="inlineStr">
@@ -11942,7 +11944,7 @@
       <c r="C294" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D294" s="11" t="n">
+      <c r="D294" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E294" s="9" t="inlineStr">
@@ -11985,7 +11987,7 @@
       <c r="C295" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D295" s="11" t="n">
+      <c r="D295" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E295" s="9" t="inlineStr">
@@ -12028,7 +12030,7 @@
       <c r="C296" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D296" s="11" t="n">
+      <c r="D296" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E296" s="9" t="inlineStr">
@@ -12071,7 +12073,7 @@
       <c r="C297" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D297" s="11" t="n">
+      <c r="D297" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E297" s="9" t="inlineStr">
@@ -12114,7 +12116,7 @@
       <c r="C298" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D298" s="11" t="n">
+      <c r="D298" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E298" s="9" t="inlineStr">
@@ -12157,7 +12159,7 @@
       <c r="C299" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D299" s="11" t="n">
+      <c r="D299" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E299" s="9" t="inlineStr">
@@ -12200,7 +12202,7 @@
       <c r="C300" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D300" s="11" t="n">
+      <c r="D300" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E300" s="9" t="inlineStr">
@@ -12243,7 +12245,7 @@
       <c r="C301" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D301" s="11" t="n">
+      <c r="D301" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E301" s="9" t="inlineStr">
@@ -12286,7 +12288,7 @@
       <c r="C302" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D302" s="11" t="n">
+      <c r="D302" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E302" s="9" t="inlineStr">
@@ -12329,7 +12331,7 @@
       <c r="C303" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D303" s="11" t="n">
+      <c r="D303" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E303" s="9" t="inlineStr">
@@ -12372,7 +12374,7 @@
       <c r="C304" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D304" s="11" t="n">
+      <c r="D304" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E304" s="9" t="inlineStr">
@@ -12415,7 +12417,7 @@
       <c r="C305" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D305" s="11" t="n">
+      <c r="D305" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E305" s="9" t="inlineStr">
@@ -12458,7 +12460,7 @@
       <c r="C306" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D306" s="11" t="n">
+      <c r="D306" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E306" s="9" t="inlineStr">
@@ -12501,7 +12503,7 @@
       <c r="C307" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D307" s="11" t="n">
+      <c r="D307" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E307" s="9" t="inlineStr">
@@ -12544,7 +12546,7 @@
       <c r="C308" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D308" s="11" t="n">
+      <c r="D308" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E308" s="9" t="inlineStr">
@@ -12591,7 +12593,7 @@
       <c r="C309" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D309" s="11" t="n">
+      <c r="D309" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E309" s="9" t="inlineStr">
@@ -12705,7 +12707,7 @@
       <c r="C313" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D313" s="11" t="n">
+      <c r="D313" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E313" s="9" t="inlineStr">
@@ -12748,7 +12750,7 @@
       <c r="C314" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D314" s="11" t="n">
+      <c r="D314" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E314" s="9" t="inlineStr">
@@ -12866,7 +12868,7 @@
       <c r="C318" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D318" s="11" t="n">
+      <c r="D318" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E318" s="9" t="inlineStr">
@@ -12909,7 +12911,7 @@
       <c r="C319" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D319" s="11" t="n">
+      <c r="D319" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E319" s="9" t="inlineStr">
@@ -13023,7 +13025,7 @@
       <c r="C323" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D323" s="11" t="n">
+      <c r="D323" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E323" s="9" t="inlineStr">
@@ -13066,7 +13068,7 @@
       <c r="C324" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D324" s="11" t="n">
+      <c r="D324" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E324" s="9" t="inlineStr">
@@ -13180,7 +13182,7 @@
       <c r="C328" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D328" s="11" t="n">
+      <c r="D328" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E328" s="9" t="inlineStr">
@@ -13223,7 +13225,7 @@
       <c r="C329" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D329" s="11" t="n">
+      <c r="D329" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E329" s="9" t="inlineStr">
@@ -13266,7 +13268,7 @@
       <c r="C330" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D330" s="11" t="n">
+      <c r="D330" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E330" s="9" t="inlineStr">
@@ -13309,7 +13311,7 @@
       <c r="C331" s="10" t="n">
         <v>46007</v>
       </c>
-      <c r="D331" s="11" t="n">
+      <c r="D331" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E331" s="9" t="inlineStr">
@@ -13352,7 +13354,7 @@
       <c r="C332" s="10" t="n">
         <v>46014</v>
       </c>
-      <c r="D332" s="11" t="n">
+      <c r="D332" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E332" s="9" t="inlineStr">
@@ -13395,7 +13397,7 @@
       <c r="C333" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D333" s="11" t="n">
+      <c r="D333" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E333" s="9" t="inlineStr">
@@ -13438,7 +13440,7 @@
       <c r="C334" s="10" t="n">
         <v>46019</v>
       </c>
-      <c r="D334" s="11" t="n">
+      <c r="D334" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E334" s="9" t="inlineStr">
@@ -13481,7 +13483,7 @@
       <c r="C335" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D335" s="11" t="n">
+      <c r="D335" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E335" s="9" t="inlineStr">
@@ -13595,7 +13597,7 @@
       <c r="C339" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D339" s="11" t="n">
+      <c r="D339" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E339" s="9" t="inlineStr">
@@ -13709,7 +13711,7 @@
       <c r="C343" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D343" s="11" t="n">
+      <c r="D343" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E343" s="9" t="inlineStr">
@@ -13756,7 +13758,7 @@
       <c r="C344" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D344" s="11" t="n">
+      <c r="D344" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E344" s="9" t="inlineStr">
@@ -13803,7 +13805,7 @@
       <c r="C345" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D345" s="11" t="n">
+      <c r="D345" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E345" s="9" t="inlineStr">
@@ -13850,7 +13852,7 @@
       <c r="C346" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D346" s="11" t="n">
+      <c r="D346" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E346" s="9" t="inlineStr">
@@ -13897,7 +13899,7 @@
       <c r="C347" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D347" s="11" t="n">
+      <c r="D347" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E347" s="9" t="inlineStr">
@@ -13940,7 +13942,7 @@
       <c r="C348" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D348" s="11" t="n">
+      <c r="D348" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E348" s="9" t="inlineStr">
@@ -14054,7 +14056,7 @@
       <c r="C352" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D352" s="11" t="n">
+      <c r="D352" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E352" s="9" t="inlineStr">
@@ -14243,7 +14245,7 @@
       <c r="C359" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D359" s="11" t="n">
+      <c r="D359" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E359" s="9" t="inlineStr">
@@ -14290,7 +14292,7 @@
       <c r="C360" s="10" t="n">
         <v>46023</v>
       </c>
-      <c r="D360" s="11" t="n">
+      <c r="D360" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E360" s="9" t="inlineStr">
@@ -14479,7 +14481,7 @@
       <c r="C367" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D367" s="11" t="n">
+      <c r="D367" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E367" s="9" t="inlineStr">
@@ -14664,7 +14666,7 @@
       <c r="C374" s="10" t="n">
         <v>46026</v>
       </c>
-      <c r="D374" s="11" t="n">
+      <c r="D374" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E374" s="9" t="inlineStr">
@@ -14853,7 +14855,7 @@
       <c r="C381" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D381" s="11" t="n">
+      <c r="D381" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E381" s="9" t="inlineStr">
@@ -14900,7 +14902,7 @@
       <c r="C382" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D382" s="11" t="n">
+      <c r="D382" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E382" s="9" t="inlineStr">
@@ -15018,7 +15020,7 @@
       <c r="C386" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D386" s="11" t="n">
+      <c r="D386" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E386" s="9" t="inlineStr">
@@ -15136,7 +15138,7 @@
       <c r="C390" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D390" s="11" t="n">
+      <c r="D390" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E390" s="9" t="inlineStr">
@@ -15325,7 +15327,7 @@
       <c r="C397" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D397" s="11" t="n">
+      <c r="D397" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E397" s="9" t="inlineStr">
@@ -15372,7 +15374,7 @@
       <c r="C398" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D398" s="11" t="n">
+      <c r="D398" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E398" s="9" t="inlineStr">
@@ -15415,7 +15417,7 @@
       <c r="C399" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D399" s="11" t="n">
+      <c r="D399" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E399" s="9" t="inlineStr">
@@ -15462,7 +15464,7 @@
       <c r="C400" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D400" s="11" t="n">
+      <c r="D400" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E400" s="9" t="inlineStr">
@@ -15580,7 +15582,7 @@
       <c r="C404" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D404" s="11" t="n">
+      <c r="D404" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E404" s="9" t="inlineStr">
@@ -15694,7 +15696,7 @@
       <c r="C408" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D408" s="11" t="n">
+      <c r="D408" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E408" s="9" t="inlineStr">
@@ -15808,7 +15810,7 @@
       <c r="C412" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D412" s="11" t="n">
+      <c r="D412" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E412" s="9" t="inlineStr">
@@ -16068,7 +16070,7 @@
       <c r="C422" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D422" s="11" t="n">
+      <c r="D422" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E422" s="9" t="inlineStr">
@@ -16115,7 +16117,7 @@
       <c r="C423" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D423" s="11" t="n">
+      <c r="D423" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E423" s="9" t="inlineStr">
@@ -16162,7 +16164,7 @@
       <c r="C424" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D424" s="11" t="n">
+      <c r="D424" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E424" s="9" t="inlineStr">
@@ -16209,7 +16211,7 @@
       <c r="C425" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D425" s="11" t="n">
+      <c r="D425" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E425" s="9" t="inlineStr">
@@ -16327,7 +16329,7 @@
       <c r="C429" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D429" s="11" t="n">
+      <c r="D429" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E429" s="9" t="inlineStr">
@@ -16445,7 +16447,7 @@
       <c r="C433" s="10" t="n">
         <v>46031</v>
       </c>
-      <c r="D433" s="11" t="n">
+      <c r="D433" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E433" s="9" t="inlineStr">
@@ -16563,7 +16565,7 @@
       <c r="C437" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D437" s="11" t="n">
+      <c r="D437" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E437" s="9" t="inlineStr">
@@ -16610,7 +16612,7 @@
       <c r="C438" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D438" s="11" t="n">
+      <c r="D438" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E438" s="9" t="inlineStr">
@@ -16653,7 +16655,7 @@
       <c r="C439" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D439" s="11" t="n">
+      <c r="D439" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E439" s="9" t="inlineStr">
@@ -16771,7 +16773,7 @@
       <c r="C443" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D443" s="11" t="n">
+      <c r="D443" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E443" s="9" t="inlineStr">
@@ -16889,7 +16891,7 @@
       <c r="C447" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D447" s="11" t="n">
+      <c r="D447" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E447" s="9" t="inlineStr">
@@ -17003,7 +17005,7 @@
       <c r="C451" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D451" s="11" t="n">
+      <c r="D451" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E451" s="9" t="inlineStr">
@@ -17108,2464 +17110,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F124"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11.4285714285714" customWidth="1" min="1" max="1"/>
-    <col width="37.1428571428571" customWidth="1" min="2" max="2"/>
-    <col width="17.1428571428571" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Storsafe Management Solutions - Cary (sms-cary)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Cash Flow Statement</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Period = Jan 2025-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Book = Accrual ; Tree = ysi_cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="24" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Period to Date</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Year to Date</t>
-        </is>
-      </c>
-      <c r="F5" s="24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>4000-0000</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> INCOME</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="28" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="28" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="28" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>4100-0000</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RENT INCOME</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>4500-1001</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Storage Rent</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>391642.32</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>391642.32</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>4710-0000</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Less: Concessions</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>-10513.71</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>-10513.71</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>4710-0006</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Bad Debt Write Off</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>-29</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>-29</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>4710-0007</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Less: Discount - Rent</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>-141</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>-141</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>4990-0000</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            NET RENT INCOME</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="n">
-        <v>380958.61</v>
-      </c>
-      <c r="D13" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>380958.61</v>
-      </c>
-      <c r="F13" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>5000-0001</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Merchandise Income</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>1099.45</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>1099.45</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>5000-0002</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Merchandise COGS</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>-1193.1</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>-1193.1</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>5000-0003</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Net Merchandise Sales</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="n">
-        <v>-93.65000000000001</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>-93.65000000000001</v>
-      </c>
-      <c r="F16" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>5000-0010</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Tenant Protection Income</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>12939.45</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>12939.45</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>5000-0011</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Tenant Protection COGS</t>
-        </is>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>-2178.48</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>-2178.48</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>5000-0012</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Net Tenant Protection Income</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="n">
-        <v>10760.97</v>
-      </c>
-      <c r="D19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>10760.97</v>
-      </c>
-      <c r="F19" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>5000-0013</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Phone Convenience Fee</t>
-        </is>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>63</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>63</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>5000-1000</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL ANCILLARY INCOME</t>
-        </is>
-      </c>
-      <c r="C21" s="30" t="n">
-        <v>10730.32</v>
-      </c>
-      <c r="D21" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="30" t="n">
-        <v>10730.32</v>
-      </c>
-      <c r="F21" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>5600-0000</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    OTHER INCOME</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>5800-0000</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Late Fee</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="n">
-        <v>4415.5</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>4415.5</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>5805-0000</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Administrative Fee</t>
-        </is>
-      </c>
-      <c r="C25" s="29" t="n">
-        <v>3637</v>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="29" t="n">
-        <v>3637</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>5890-0000</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL OTHER INCOME</t>
-        </is>
-      </c>
-      <c r="C26" s="30" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="D26" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="30" t="n">
-        <v>8052.5</v>
-      </c>
-      <c r="F26" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>5990-0000</t>
-        </is>
-      </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                TOTAL INCOME</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="n">
-        <v>399741.43</v>
-      </c>
-      <c r="D28" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="34" t="n">
-        <v>399741.43</v>
-      </c>
-      <c r="F28" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="28" t="n"/>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n"/>
-      <c r="E29" s="28" t="n"/>
-      <c r="F29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>6000-0000</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> EXPENSES</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="n"/>
-      <c r="D30" s="35" t="n"/>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="35" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="28" t="n"/>
-      <c r="F31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>6050-0000</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ADVERTISING and MARKETING</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>6050-0010</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Advertising</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>288.84</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>288.84</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>6050-0025</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Internet Marketing</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>11296.1</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>11296.1</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>6050-0026</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        OnSite Marketing</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>1480.08</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>1480.08</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>6050-0030</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Marketing Other</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="D36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="29" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="F36" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>6050-9999</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            ADVERTISING and MARKETING TOTAL</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="n">
-        <v>13097.07</v>
-      </c>
-      <c r="D37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="30" t="n">
-        <v>13097.07</v>
-      </c>
-      <c r="F37" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="28" t="n"/>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>6100-0000</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    REPAIRS AND MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>6110-1050</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Repairs and  Maintenance</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>5728.41</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>5728.41</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="28" t="inlineStr">
-        <is>
-          <t>6110-1060</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Maintenance Tools and Supplies</t>
-        </is>
-      </c>
-      <c r="C41" s="29" t="n">
-        <v>135.2</v>
-      </c>
-      <c r="D41" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="29" t="n">
-        <v>135.2</v>
-      </c>
-      <c r="F41" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
-        <is>
-          <t>6199-9999</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL REPAIRS AND MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C42" s="30" t="n">
-        <v>5863.61</v>
-      </c>
-      <c r="D42" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="30" t="n">
-        <v>5863.61</v>
-      </c>
-      <c r="F42" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="28" t="n"/>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="28" t="n"/>
-      <c r="D43" s="28" t="n"/>
-      <c r="E43" s="28" t="n"/>
-      <c r="F43" s="28" t="n"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="28" t="inlineStr">
-        <is>
-          <t>6200-0000</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    GROUNDS</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="28" t="inlineStr">
-        <is>
-          <t>6200-0001</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Trash Disposal</t>
-        </is>
-      </c>
-      <c r="C45" s="29" t="n">
-        <v>4624.92</v>
-      </c>
-      <c r="D45" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="29" t="n">
-        <v>4624.92</v>
-      </c>
-      <c r="F45" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>6299-9999</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL GROUNDS</t>
-        </is>
-      </c>
-      <c r="C46" s="30" t="n">
-        <v>4624.92</v>
-      </c>
-      <c r="D46" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="30" t="n">
-        <v>4624.92</v>
-      </c>
-      <c r="F46" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="28" t="n"/>
-      <c r="B47" s="9" t="n"/>
-      <c r="C47" s="28" t="n"/>
-      <c r="D47" s="28" t="n"/>
-      <c r="E47" s="28" t="n"/>
-      <c r="F47" s="28" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="28" t="inlineStr">
-        <is>
-          <t>6300-0000</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    SECURITY SAFETY OTHER EXPENSE</t>
-        </is>
-      </c>
-      <c r="C48" s="18" t="n"/>
-      <c r="D48" s="18" t="n"/>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="28" t="inlineStr">
-        <is>
-          <t>6310-0000</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Fire and Life Safety Maintenance</t>
-        </is>
-      </c>
-      <c r="C49" s="29" t="n">
-        <v>200</v>
-      </c>
-      <c r="D49" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="29" t="n">
-        <v>200</v>
-      </c>
-      <c r="F49" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>6375-0000</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL SECURITY SAFETY OTHER EXPENSES</t>
-        </is>
-      </c>
-      <c r="C50" s="30" t="n">
-        <v>200</v>
-      </c>
-      <c r="D50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="30" t="n">
-        <v>200</v>
-      </c>
-      <c r="F50" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="28" t="n"/>
-      <c r="B51" s="9" t="n"/>
-      <c r="C51" s="28" t="n"/>
-      <c r="D51" s="28" t="n"/>
-      <c r="E51" s="28" t="n"/>
-      <c r="F51" s="28" t="n"/>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>6400-0000</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    UTILITIES</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="n"/>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="18" t="n"/>
-      <c r="F52" s="18" t="n"/>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="28" t="inlineStr">
-        <is>
-          <t>6400-0046</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Internet Services</t>
-        </is>
-      </c>
-      <c r="C53" s="12" t="n">
-        <v>2690.74</v>
-      </c>
-      <c r="D53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="12" t="n">
-        <v>2690.74</v>
-      </c>
-      <c r="F53" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="28" t="inlineStr">
-        <is>
-          <t>6400-0047</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Telephone Service</t>
-        </is>
-      </c>
-      <c r="C54" s="29" t="n">
-        <v>120.96</v>
-      </c>
-      <c r="D54" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="29" t="n">
-        <v>120.96</v>
-      </c>
-      <c r="F54" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="28" t="inlineStr">
-        <is>
-          <t>6425-0000</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL UTILITIES</t>
-        </is>
-      </c>
-      <c r="C55" s="30" t="n">
-        <v>2811.7</v>
-      </c>
-      <c r="D55" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="30" t="n">
-        <v>2811.7</v>
-      </c>
-      <c r="F55" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="28" t="inlineStr">
-        <is>
-          <t>6450-0010</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Management Fee</t>
-        </is>
-      </c>
-      <c r="C56" s="29" t="n">
-        <v>19337.92</v>
-      </c>
-      <c r="D56" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="29" t="n">
-        <v>19337.92</v>
-      </c>
-      <c r="F56" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="28" t="inlineStr">
-        <is>
-          <t>6455-0000</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL ADMINISTRATIVE &amp; MANAGEMENT EXPENSES</t>
-        </is>
-      </c>
-      <c r="C57" s="30" t="n">
-        <v>19337.92</v>
-      </c>
-      <c r="D57" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="30" t="n">
-        <v>19337.92</v>
-      </c>
-      <c r="F57" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="28" t="inlineStr">
-        <is>
-          <t>6461-0000</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Property Tax</t>
-        </is>
-      </c>
-      <c r="C58" s="12" t="n">
-        <v>58002.24</v>
-      </c>
-      <c r="D58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="12" t="n">
-        <v>58002.24</v>
-      </c>
-      <c r="F58" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="28" t="inlineStr">
-        <is>
-          <t>6461-1000</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Property Insurance</t>
-        </is>
-      </c>
-      <c r="C59" s="29" t="n">
-        <v>7310.7</v>
-      </c>
-      <c r="D59" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="29" t="n">
-        <v>7310.7</v>
-      </c>
-      <c r="F59" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="28" t="inlineStr">
-        <is>
-          <t>6470-0000</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PROPERTY TAXES &amp; INSURANCE</t>
-        </is>
-      </c>
-      <c r="C60" s="30" t="n">
-        <v>65312.94</v>
-      </c>
-      <c r="D60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="30" t="n">
-        <v>65312.94</v>
-      </c>
-      <c r="F60" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>7000-0013</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Vehicle Expense</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="n">
-        <v>716.15</v>
-      </c>
-      <c r="D61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="12" t="n">
-        <v>716.15</v>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>7000-0026</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Software</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="n">
-        <v>5880.78</v>
-      </c>
-      <c r="D62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="12" t="n">
-        <v>5880.78</v>
-      </c>
-      <c r="F62" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="28" t="inlineStr">
-        <is>
-          <t>7000-0045</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Bank Charges Expense</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="n">
-        <v>4132.86</v>
-      </c>
-      <c r="D63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="12" t="n">
-        <v>4132.86</v>
-      </c>
-      <c r="F63" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>7000-0047</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Credit Card Processing Fees</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="n">
-        <v>9320.02</v>
-      </c>
-      <c r="D64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="12" t="n">
-        <v>9320.02</v>
-      </c>
-      <c r="F64" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="28" t="inlineStr">
-        <is>
-          <t>7000-0050</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Postage and Shipping Fees</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="n">
-        <v>286.93</v>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="12" t="n">
-        <v>286.93</v>
-      </c>
-      <c r="F65" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="28" t="inlineStr">
-        <is>
-          <t>7000-0054</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Travel Expenses</t>
-        </is>
-      </c>
-      <c r="C66" s="29" t="n">
-        <v>104.48</v>
-      </c>
-      <c r="D66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="29" t="n">
-        <v>104.48</v>
-      </c>
-      <c r="F66" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>7000-1000</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL G and A EXPENSE</t>
-        </is>
-      </c>
-      <c r="C67" s="30" t="n">
-        <v>20441.22</v>
-      </c>
-      <c r="D67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="30" t="n">
-        <v>20441.22</v>
-      </c>
-      <c r="F67" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="28" t="n"/>
-      <c r="B68" s="9" t="n"/>
-      <c r="C68" s="28" t="n"/>
-      <c r="D68" s="28" t="n"/>
-      <c r="E68" s="28" t="n"/>
-      <c r="F68" s="28" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>7200-0000</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    PROFESSIONAL FEES</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>7200-0001</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Answering Service</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="n">
-        <v>-117.06</v>
-      </c>
-      <c r="D70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="12" t="n">
-        <v>-117.06</v>
-      </c>
-      <c r="F70" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="28" t="inlineStr">
-        <is>
-          <t>7200-0002</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Communication Center</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="n">
-        <v>7954.47</v>
-      </c>
-      <c r="D71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="12" t="n">
-        <v>7954.47</v>
-      </c>
-      <c r="F71" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>7200-0003</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Auction Costs</t>
-        </is>
-      </c>
-      <c r="C72" s="12" t="n">
-        <v>1764.79</v>
-      </c>
-      <c r="D72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="12" t="n">
-        <v>1764.79</v>
-      </c>
-      <c r="F72" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="28" t="inlineStr">
-        <is>
-          <t>7200-0020</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Professional Fees</t>
-        </is>
-      </c>
-      <c r="C73" s="29" t="n">
-        <v>176</v>
-      </c>
-      <c r="D73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="29" t="n">
-        <v>176</v>
-      </c>
-      <c r="F73" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="28" t="inlineStr">
-        <is>
-          <t>7200-0100</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PROFESSIONAL FEES</t>
-        </is>
-      </c>
-      <c r="C74" s="30" t="n">
-        <v>9778.200000000001</v>
-      </c>
-      <c r="D74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="30" t="n">
-        <v>9778.200000000001</v>
-      </c>
-      <c r="F74" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="28" t="n"/>
-      <c r="B75" s="9" t="n"/>
-      <c r="C75" s="28" t="n"/>
-      <c r="D75" s="28" t="n"/>
-      <c r="E75" s="28" t="n"/>
-      <c r="F75" s="28" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>7310-0000</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SUPERVISORY PAYROLL</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="n"/>
-      <c r="D76" s="18" t="n"/>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>7310-0005</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Supervisory Payroll Expense</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="D77" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="29" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="F77" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>7310-0100</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL SUPERVISORY PAYROLL</t>
-        </is>
-      </c>
-      <c r="C78" s="36" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="D78" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="36" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="F78" s="36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="28" t="inlineStr">
-        <is>
-          <t>7500-0000</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PAYROLL</t>
-        </is>
-      </c>
-      <c r="C79" s="30" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="D79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="30" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="F79" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="28" t="n"/>
-      <c r="B80" s="9" t="n"/>
-      <c r="C80" s="31" t="n"/>
-      <c r="D80" s="31" t="n"/>
-      <c r="E80" s="31" t="n"/>
-      <c r="F80" s="31" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="32" t="inlineStr">
-        <is>
-          <t>7999-9000</t>
-        </is>
-      </c>
-      <c r="B81" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL NET OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="C81" s="34" t="n">
-        <v>146495.12</v>
-      </c>
-      <c r="D81" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="34" t="n">
-        <v>146495.12</v>
-      </c>
-      <c r="F81" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="28" t="n"/>
-      <c r="B82" s="9" t="n"/>
-      <c r="C82" s="37" t="n"/>
-      <c r="D82" s="37" t="n"/>
-      <c r="E82" s="37" t="n"/>
-      <c r="F82" s="37" t="n"/>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="38" t="inlineStr">
-        <is>
-          <t>7999-9999</t>
-        </is>
-      </c>
-      <c r="B83" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NET OPERATING INCOME</t>
-        </is>
-      </c>
-      <c r="C83" s="40" t="n">
-        <v>253246.31</v>
-      </c>
-      <c r="D83" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="40" t="n">
-        <v>253246.31</v>
-      </c>
-      <c r="F83" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="28" t="inlineStr">
-        <is>
-          <t>8179-9999</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Repairs Major</t>
-        </is>
-      </c>
-      <c r="C84" s="41" t="n">
-        <v>3047.56</v>
-      </c>
-      <c r="D84" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="41" t="n">
-        <v>3047.56</v>
-      </c>
-      <c r="F84" s="41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="28" t="inlineStr">
-        <is>
-          <t>8389-9999</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Miscelleneous Non-Operating Expense</t>
-        </is>
-      </c>
-      <c r="C85" s="29" t="n">
-        <v>1641.95</v>
-      </c>
-      <c r="D85" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="29" t="n">
-        <v>1641.95</v>
-      </c>
-      <c r="F85" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="28" t="inlineStr">
-        <is>
-          <t>8390-0000</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL NON-RECURRING EXPENSES</t>
-        </is>
-      </c>
-      <c r="C86" s="30" t="n">
-        <v>4689.51</v>
-      </c>
-      <c r="D86" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="30" t="n">
-        <v>4689.51</v>
-      </c>
-      <c r="F86" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="28" t="inlineStr">
-        <is>
-          <t>8540-0000</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Loan Interest</t>
-        </is>
-      </c>
-      <c r="C87" s="29" t="n">
-        <v>130408.08</v>
-      </c>
-      <c r="D87" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="29" t="n">
-        <v>130408.08</v>
-      </c>
-      <c r="F87" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="28" t="inlineStr">
-        <is>
-          <t>8590-0000</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL LOAN INTEREST</t>
-        </is>
-      </c>
-      <c r="C88" s="30" t="n">
-        <v>130408.08</v>
-      </c>
-      <c r="D88" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="30" t="n">
-        <v>130408.08</v>
-      </c>
-      <c r="F88" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="28" t="n"/>
-      <c r="B89" s="9" t="n"/>
-      <c r="C89" s="31" t="n"/>
-      <c r="D89" s="31" t="n"/>
-      <c r="E89" s="31" t="n"/>
-      <c r="F89" s="31" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="32" t="inlineStr">
-        <is>
-          <t>8990-0000</t>
-        </is>
-      </c>
-      <c r="B90" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="C90" s="34" t="n">
-        <v>135097.59</v>
-      </c>
-      <c r="D90" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="34" t="n">
-        <v>135097.59</v>
-      </c>
-      <c r="F90" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="28" t="n"/>
-      <c r="B91" s="9" t="n"/>
-      <c r="C91" s="37" t="n"/>
-      <c r="D91" s="37" t="n"/>
-      <c r="E91" s="37" t="n"/>
-      <c r="F91" s="37" t="n"/>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="32" t="inlineStr">
-        <is>
-          <t>9090-0000</t>
-        </is>
-      </c>
-      <c r="B92" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NET INCOME</t>
-        </is>
-      </c>
-      <c r="C92" s="42" t="n">
-        <v>118148.72</v>
-      </c>
-      <c r="D92" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="42" t="n">
-        <v>118148.72</v>
-      </c>
-      <c r="F92" s="42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="28" t="n"/>
-      <c r="B93" s="9" t="n"/>
-      <c r="C93" s="43" t="n"/>
-      <c r="D93" s="43" t="n"/>
-      <c r="E93" s="43" t="n"/>
-      <c r="F93" s="43" t="n"/>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="28" t="n"/>
-      <c r="B94" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="C94" s="18" t="n"/>
-      <c r="D94" s="18" t="n"/>
-      <c r="E94" s="18" t="n"/>
-      <c r="F94" s="18" t="n"/>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="28" t="n"/>
-      <c r="B95" s="9" t="n"/>
-      <c r="C95" s="28" t="n"/>
-      <c r="D95" s="28" t="n"/>
-      <c r="E95" s="28" t="n"/>
-      <c r="F95" s="28" t="n"/>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="28" t="inlineStr">
-        <is>
-          <t>1300-0000</t>
-        </is>
-      </c>
-      <c r="B96" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="n">
-        <v>-10361.75</v>
-      </c>
-      <c r="D96" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>-10361.75</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="28" t="inlineStr">
-        <is>
-          <t>1350-0001</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Pre-Paid Insurance</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="n">
-        <v>635.7</v>
-      </c>
-      <c r="D97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>635.7</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="28" t="inlineStr">
-        <is>
-          <t>2110-0000</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Note 1 Principal</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="n">
-        <v>-17813.16</v>
-      </c>
-      <c r="D98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="12" t="n">
-        <v>-17813.16</v>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="28" t="inlineStr">
-        <is>
-          <t>2150-0020</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Due To/(From) Other Property</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="n">
-        <v>-13655.53</v>
-      </c>
-      <c r="D99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>-13655.53</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="28" t="inlineStr">
-        <is>
-          <t>2200-0000</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
-        <v>3904.21</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>3904.21</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="28" t="inlineStr">
-        <is>
-          <t>2210-0000</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Prepaid Rent</t>
-        </is>
-      </c>
-      <c r="C101" s="29" t="n">
-        <v>-2939.68</v>
-      </c>
-      <c r="D101" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="29" t="n">
-        <v>-2939.68</v>
-      </c>
-      <c r="F101" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="28" t="inlineStr">
-        <is>
-          <t>2250-0000</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Tenant Deposits</t>
-        </is>
-      </c>
-      <c r="C102" s="30" t="n">
-        <v>600</v>
-      </c>
-      <c r="D102" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="30" t="n">
-        <v>600</v>
-      </c>
-      <c r="F102" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="28" t="inlineStr">
-        <is>
-          <t>2305-0000</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Real Estate Tax Accrual</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="n">
-        <v>8114.2</v>
-      </c>
-      <c r="D103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>8114.2</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="28" t="inlineStr">
-        <is>
-          <t>2310-0000</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Sales Tax Collected</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="n">
-        <v>5826.84</v>
-      </c>
-      <c r="D104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="12" t="n">
-        <v>5826.84</v>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="28" t="inlineStr">
-        <is>
-          <t>2640-0998</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Expense Accrual</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="n">
-        <v>2478.43</v>
-      </c>
-      <c r="D105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>2478.43</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="28" t="inlineStr">
-        <is>
-          <t>2640-0999</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Payroll Accrual</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="n">
-        <v>27.48</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>27.48</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="28" t="inlineStr">
-        <is>
-          <t>3300-0000</t>
-        </is>
-      </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Owner Distributions</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="n">
-        <v>-102655.07</v>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>-102655.07</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="28" t="inlineStr">
-        <is>
-          <t>7200-0003</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Auction Costs</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="n">
-        <v>-1764.79</v>
-      </c>
-      <c r="D108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>-1764.79</v>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="28" t="n"/>
-      <c r="B109" s="9" t="n"/>
-      <c r="C109" s="31" t="n"/>
-      <c r="D109" s="31" t="n"/>
-      <c r="E109" s="31" t="n"/>
-      <c r="F109" s="31" t="n"/>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="28" t="n"/>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="C110" s="30" t="n">
-        <v>-127603.12</v>
-      </c>
-      <c r="D110" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="30" t="n">
-        <v>-127603.12</v>
-      </c>
-      <c r="F110" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="28" t="n"/>
-      <c r="B111" s="9" t="n"/>
-      <c r="C111" s="31" t="n"/>
-      <c r="D111" s="31" t="n"/>
-      <c r="E111" s="31" t="n"/>
-      <c r="F111" s="31" t="n"/>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="28" t="n"/>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    CASH FLOW</t>
-        </is>
-      </c>
-      <c r="C112" s="30" t="n">
-        <v>-9454.4</v>
-      </c>
-      <c r="D112" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="30" t="n">
-        <v>-9454.4</v>
-      </c>
-      <c r="F112" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="28" t="n"/>
-    </row>
-    <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="28" t="n"/>
-      <c r="B114" s="33" t="inlineStr">
-        <is>
-          <t>Period to Date</t>
-        </is>
-      </c>
-      <c r="C114" s="32" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="D114" s="32" t="inlineStr">
-        <is>
-          <t>Ending Balance</t>
-        </is>
-      </c>
-      <c r="E114" s="32" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="F114" s="28" t="n"/>
-    </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="28" t="inlineStr">
-        <is>
-          <t>1110-4909</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>EP MSS 1st Merchants</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" s="28" t="n"/>
-    </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="28" t="inlineStr">
-        <is>
-          <t>1110-4925</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>Storsafe of Cary Chase</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" s="28" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="28" t="inlineStr">
-        <is>
-          <t>1110-4971</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>Storsafe Management Solutions - Cary</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="n">
-        <v>46080.46</v>
-      </c>
-      <c r="D117" s="12" t="n">
-        <v>38390.85</v>
-      </c>
-      <c r="E117" s="12" t="n">
-        <v>-7689.61</v>
-      </c>
-      <c r="F117" s="28" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="28" t="n"/>
-      <c r="B118" s="33" t="inlineStr">
-        <is>
-          <t>Total Cash</t>
-        </is>
-      </c>
-      <c r="C118" s="44" t="n">
-        <v>46080.46</v>
-      </c>
-      <c r="D118" s="44" t="n">
-        <v>38390.85</v>
-      </c>
-      <c r="E118" s="44" t="n">
-        <v>-7689.61</v>
-      </c>
-      <c r="F118" s="28" t="n"/>
-    </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="28" t="n"/>
-    </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="28" t="n"/>
-      <c r="B120" s="33" t="inlineStr">
-        <is>
-          <t>Year to Date</t>
-        </is>
-      </c>
-      <c r="C120" s="32" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="D120" s="32" t="inlineStr">
-        <is>
-          <t>Ending Balance</t>
-        </is>
-      </c>
-      <c r="E120" s="32" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="F120" s="28" t="n"/>
-    </row>
-    <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="28" t="inlineStr">
-        <is>
-          <t>1110-4909</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>EP MSS 1st Merchants</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" s="28" t="n"/>
-    </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="28" t="inlineStr">
-        <is>
-          <t>1110-4925</t>
-        </is>
-      </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>Storsafe of Cary Chase</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" s="28" t="n"/>
-    </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="28" t="inlineStr">
-        <is>
-          <t>1110-4971</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>Storsafe Management Solutions - Cary</t>
-        </is>
-      </c>
-      <c r="C123" s="12" t="n">
-        <v>46080.46</v>
-      </c>
-      <c r="D123" s="12" t="n">
-        <v>38390.85</v>
-      </c>
-      <c r="E123" s="12" t="n">
-        <v>-7689.61</v>
-      </c>
-      <c r="F123" s="28" t="n"/>
-    </row>
-    <row r="124" ht="15" customHeight="1">
-      <c r="A124" s="28" t="n"/>
-      <c r="B124" s="33" t="inlineStr">
-        <is>
-          <t>Total Cash</t>
-        </is>
-      </c>
-      <c r="C124" s="44" t="n">
-        <v>46080.46</v>
-      </c>
-      <c r="D124" s="44" t="n">
-        <v>38390.85</v>
-      </c>
-      <c r="E124" s="44" t="n">
-        <v>-7689.61</v>
-      </c>
-      <c r="F124" s="28" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A119:F119"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="990" firstPageNumber="1" useFirstPageNumber="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23405,4 +20949,2429 @@
   <pageMargins left="0.7" right="0.7" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="5" fitToHeight="990" firstPageNumber="1" useFirstPageNumber="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F123"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="12.75"/>
+  <cols>
+    <col width="11.4285714285714" customWidth="1" min="1" max="1"/>
+    <col width="37.1428571428571" customWidth="1" min="2" max="2"/>
+    <col width="17.1428571428571" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Storsafe Management Solutions - Cary (sms-cary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cash Flow Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Period = Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Book = Accrual ; Tree = ysi_cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="24" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Period to Date</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Year to Date</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>4000-0000</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> INCOME</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="27" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="28" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>4100-0000</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RENT INCOME</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>4500-1001</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Storage Rent</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>32867.14</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>391642.32</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>4710-0000</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Less: Concessions</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>-190.88</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>-10513.71</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>4710-0006</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Bad Debt Write Off</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>-29</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>-29</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>4710-0007</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Less: Discount - Rent</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>-141</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>-141</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>4990-0000</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            NET RENT INCOME</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>32506.26</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>380958.61</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>5000-0001</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Merchandise Income</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>1099.45</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>5000-0002</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Merchandise COGS</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>-1193.1</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>5000-0003</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Net Merchandise Sales</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>-80.01000000000001</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>-93.65000000000001</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>5000-0010</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Tenant Protection Income</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>1090.1</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>12939.45</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>5000-0011</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Tenant Protection COGS</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>-150.62</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>-2178.48</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>5000-0012</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Net Tenant Protection Income</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>939.48</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>10760.97</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>5000-0013</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Phone Convenience Fee</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>63</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>5000-1000</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL ANCILLARY INCOME</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>873.47</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>10730.32</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>5600-0000</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>5800-0000</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Late Fee</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>4415.5</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>5805-0000</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Administrative Fee</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="n">
+        <v>319</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="29" t="n">
+        <v>3637</v>
+      </c>
+      <c r="F25" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>5890-0000</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>405</v>
+      </c>
+      <c r="D26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>8052.5</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>5990-0000</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>33784.73</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="34" t="n">
+        <v>399741.43</v>
+      </c>
+      <c r="F28" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="28" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>6000-0000</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> EXPENSES</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="35" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>6050-0000</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADVERTISING and MARKETING</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>6050-0010</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Advertising</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>250.8</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>288.84</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>6050-0025</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Internet Marketing</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>921.61</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>11296.1</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>6050-0026</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        OnSite Marketing</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>123.34</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>1480.08</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>6050-0030</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Marketing Other</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="F36" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>6050-9999</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            ADVERTISING and MARKETING TOTAL</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>1295.75</v>
+      </c>
+      <c r="D37" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>13097.07</v>
+      </c>
+      <c r="F37" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="28" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>6100-0000</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    REPAIRS AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>6110-1050</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Repairs and  Maintenance</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>948</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>5728.41</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>6110-1060</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Maintenance Tools and Supplies</t>
+        </is>
+      </c>
+      <c r="C41" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>135.2</v>
+      </c>
+      <c r="F41" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>6199-9999</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL REPAIRS AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="n">
+        <v>948</v>
+      </c>
+      <c r="D42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>5863.61</v>
+      </c>
+      <c r="F42" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="28" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="28" t="n"/>
+      <c r="D43" s="28" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="28" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>6200-0000</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUNDS</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>6200-0001</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Trash Disposal</t>
+        </is>
+      </c>
+      <c r="C45" s="29" t="n">
+        <v>577.0599999999999</v>
+      </c>
+      <c r="D45" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="29" t="n">
+        <v>4624.92</v>
+      </c>
+      <c r="F45" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>6299-9999</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL GROUNDS</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="n">
+        <v>577.0599999999999</v>
+      </c>
+      <c r="D46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>4624.92</v>
+      </c>
+      <c r="F46" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="28" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="28" t="n"/>
+      <c r="D47" s="28" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="28" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>6300-0000</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    SECURITY SAFETY OTHER EXPENSE</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>6310-0000</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Fire and Life Safety Maintenance</t>
+        </is>
+      </c>
+      <c r="C49" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="29" t="n">
+        <v>200</v>
+      </c>
+      <c r="F49" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>6375-0000</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL SECURITY SAFETY OTHER EXPENSES</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="F50" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="28" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="28" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="28" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>6400-0000</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UTILITIES</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>6400-0046</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Internet Services</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="n">
+        <v>262.93</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="12" t="n">
+        <v>2690.74</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>6400-0047</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Telephone Service</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="29" t="n">
+        <v>120.96</v>
+      </c>
+      <c r="F54" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>6425-0000</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL UTILITIES</t>
+        </is>
+      </c>
+      <c r="C55" s="30" t="n">
+        <v>262.93</v>
+      </c>
+      <c r="D55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="30" t="n">
+        <v>2811.7</v>
+      </c>
+      <c r="F55" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>6450-0010</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Management Fee</t>
+        </is>
+      </c>
+      <c r="C56" s="29" t="n">
+        <v>1648.95</v>
+      </c>
+      <c r="D56" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="29" t="n">
+        <v>19337.92</v>
+      </c>
+      <c r="F56" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>6455-0000</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL ADMINISTRATIVE &amp; MANAGEMENT EXPENSES</t>
+        </is>
+      </c>
+      <c r="C57" s="30" t="n">
+        <v>1648.95</v>
+      </c>
+      <c r="D57" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="30" t="n">
+        <v>19337.92</v>
+      </c>
+      <c r="F57" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>6461-0000</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Property Tax</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="n">
+        <v>4833.52</v>
+      </c>
+      <c r="D58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>58002.24</v>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>6461-1000</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Property Insurance</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="n">
+        <v>556.25</v>
+      </c>
+      <c r="D59" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="29" t="n">
+        <v>7310.7</v>
+      </c>
+      <c r="F59" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>6470-0000</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PROPERTY TAXES &amp; INSURANCE</t>
+        </is>
+      </c>
+      <c r="C60" s="30" t="n">
+        <v>5389.77</v>
+      </c>
+      <c r="D60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="30" t="n">
+        <v>65312.94</v>
+      </c>
+      <c r="F60" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>7000-0013</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Vehicle Expense</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>716.15</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>7000-0026</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Software</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="n">
+        <v>596.02</v>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>5880.78</v>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t>7000-0045</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Bank Charges Expense</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="n">
+        <v>289.18</v>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>4132.86</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>7000-0047</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Credit Card Processing Fees</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="n">
+        <v>918.6900000000001</v>
+      </c>
+      <c r="D64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>9320.02</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>7000-0050</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Postage and Shipping Fees</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>286.93</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>7000-0054</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Travel Expenses</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="29" t="n">
+        <v>104.48</v>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>7000-1000</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL G and A EXPENSE</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="n">
+        <v>1848.89</v>
+      </c>
+      <c r="D67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="30" t="n">
+        <v>20441.22</v>
+      </c>
+      <c r="F67" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="28" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="28" t="n"/>
+      <c r="D68" s="28" t="n"/>
+      <c r="E68" s="28" t="n"/>
+      <c r="F68" s="28" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>7200-0000</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PROFESSIONAL FEES</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>7200-0001</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Answering Service</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>-117.06</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>7200-0002</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Communication Center</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="n">
+        <v>626.9400000000001</v>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>7954.47</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>7200-0003</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Auction Costs</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>1764.79</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>7200-0020</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Professional Fees</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="D73" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="29" t="n">
+        <v>176</v>
+      </c>
+      <c r="F73" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>7200-0100</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PROFESSIONAL FEES</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="n">
+        <v>645.9400000000001</v>
+      </c>
+      <c r="D74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="30" t="n">
+        <v>9778.200000000001</v>
+      </c>
+      <c r="F74" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="28" t="n"/>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="28" t="n"/>
+      <c r="D75" s="28" t="n"/>
+      <c r="E75" s="28" t="n"/>
+      <c r="F75" s="28" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>7310-0000</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SUPERVISORY PAYROLL</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="18" t="n"/>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>7310-0005</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Supervisory Payroll Expense</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="n">
+        <v>439.57</v>
+      </c>
+      <c r="D77" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="29" t="n">
+        <v>5027.54</v>
+      </c>
+      <c r="F77" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>7310-0100</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL SUPERVISORY PAYROLL</t>
+        </is>
+      </c>
+      <c r="C78" s="36" t="n">
+        <v>439.57</v>
+      </c>
+      <c r="D78" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="36" t="n">
+        <v>5027.54</v>
+      </c>
+      <c r="F78" s="36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>7500-0000</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PAYROLL</t>
+        </is>
+      </c>
+      <c r="C79" s="30" t="n">
+        <v>439.57</v>
+      </c>
+      <c r="D79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="30" t="n">
+        <v>5027.54</v>
+      </c>
+      <c r="F79" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="28" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="31" t="n"/>
+      <c r="D80" s="31" t="n"/>
+      <c r="E80" s="31" t="n"/>
+      <c r="F80" s="31" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>7999-9000</t>
+        </is>
+      </c>
+      <c r="B81" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL NET OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C81" s="34" t="n">
+        <v>13056.86</v>
+      </c>
+      <c r="D81" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="34" t="n">
+        <v>146495.12</v>
+      </c>
+      <c r="F81" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="28" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="37" t="n"/>
+      <c r="D82" s="37" t="n"/>
+      <c r="E82" s="37" t="n"/>
+      <c r="F82" s="37" t="n"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="38" t="inlineStr">
+        <is>
+          <t>7999-9999</t>
+        </is>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NET OPERATING INCOME</t>
+        </is>
+      </c>
+      <c r="C83" s="40" t="n">
+        <v>20727.87</v>
+      </c>
+      <c r="D83" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="40" t="n">
+        <v>253246.31</v>
+      </c>
+      <c r="F83" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="28" t="inlineStr">
+        <is>
+          <t>8179-9999</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Repairs Major</t>
+        </is>
+      </c>
+      <c r="C84" s="41" t="n">
+        <v>1703.45</v>
+      </c>
+      <c r="D84" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="41" t="n">
+        <v>3047.56</v>
+      </c>
+      <c r="F84" s="41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="28" t="inlineStr">
+        <is>
+          <t>8389-9999</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Miscelleneous Non-Operating Expense</t>
+        </is>
+      </c>
+      <c r="C85" s="29" t="n">
+        <v>39.95</v>
+      </c>
+      <c r="D85" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="29" t="n">
+        <v>1641.95</v>
+      </c>
+      <c r="F85" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="28" t="inlineStr">
+        <is>
+          <t>8390-0000</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL NON-RECURRING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C86" s="30" t="n">
+        <v>1743.4</v>
+      </c>
+      <c r="D86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="30" t="n">
+        <v>4689.51</v>
+      </c>
+      <c r="F86" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="28" t="inlineStr">
+        <is>
+          <t>8540-0000</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Loan Interest</t>
+        </is>
+      </c>
+      <c r="C87" s="29" t="n">
+        <v>10509.53</v>
+      </c>
+      <c r="D87" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="29" t="n">
+        <v>130408.08</v>
+      </c>
+      <c r="F87" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="28" t="inlineStr">
+        <is>
+          <t>8590-0000</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL LOAN INTEREST</t>
+        </is>
+      </c>
+      <c r="C88" s="30" t="n">
+        <v>10509.53</v>
+      </c>
+      <c r="D88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="30" t="n">
+        <v>130408.08</v>
+      </c>
+      <c r="F88" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="28" t="n"/>
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="31" t="n"/>
+      <c r="D89" s="31" t="n"/>
+      <c r="E89" s="31" t="n"/>
+      <c r="F89" s="31" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="32" t="inlineStr">
+        <is>
+          <t>8990-0000</t>
+        </is>
+      </c>
+      <c r="B90" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="C90" s="34" t="n">
+        <v>12252.93</v>
+      </c>
+      <c r="D90" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="34" t="n">
+        <v>135097.59</v>
+      </c>
+      <c r="F90" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="28" t="n"/>
+      <c r="B91" s="9" t="n"/>
+      <c r="C91" s="37" t="n"/>
+      <c r="D91" s="37" t="n"/>
+      <c r="E91" s="37" t="n"/>
+      <c r="F91" s="37" t="n"/>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="32" t="inlineStr">
+        <is>
+          <t>9090-0000</t>
+        </is>
+      </c>
+      <c r="B92" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NET INCOME</t>
+        </is>
+      </c>
+      <c r="C92" s="42" t="n">
+        <v>8474.940000000001</v>
+      </c>
+      <c r="D92" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="42" t="n">
+        <v>118148.72</v>
+      </c>
+      <c r="F92" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="28" t="n"/>
+      <c r="B93" s="9" t="n"/>
+      <c r="C93" s="43" t="n"/>
+      <c r="D93" s="43" t="n"/>
+      <c r="E93" s="43" t="n"/>
+      <c r="F93" s="43" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="28" t="n"/>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="n"/>
+      <c r="D94" s="18" t="n"/>
+      <c r="E94" s="18" t="n"/>
+      <c r="F94" s="18" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="28" t="n"/>
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="28" t="n"/>
+      <c r="D95" s="28" t="n"/>
+      <c r="E95" s="28" t="n"/>
+      <c r="F95" s="28" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="28" t="inlineStr">
+        <is>
+          <t>1300-0000</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="n">
+        <v>-1036.91</v>
+      </c>
+      <c r="D96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>-10361.75</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>1350-0001</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pre-Paid Insurance</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>556.25</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>635.7</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>2110-0000</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Note 1 Principal</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>-1842.24</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>-17813.16</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>2150-0020</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Due To/(From) Other Property</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>-9539.9</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>-13695.43</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>2200-0000</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Accounts Payable</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>1827</v>
+      </c>
+      <c r="D100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>3904.21</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>2210-0000</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Prepaid Rent</t>
+        </is>
+      </c>
+      <c r="C101" s="29" t="n">
+        <v>-628.26</v>
+      </c>
+      <c r="D101" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="29" t="n">
+        <v>-2939.68</v>
+      </c>
+      <c r="F101" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>2250-0000</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tenant Deposits</t>
+        </is>
+      </c>
+      <c r="C102" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="30" t="n">
+        <v>600</v>
+      </c>
+      <c r="F102" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="28" t="inlineStr">
+        <is>
+          <t>2305-0000</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Real Estate Tax Accrual</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="n">
+        <v>4833.52</v>
+      </c>
+      <c r="D103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>8114.2</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="28" t="inlineStr">
+        <is>
+          <t>2310-0000</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sales Tax Collected</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>748.54</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>5799.39</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="28" t="inlineStr">
+        <is>
+          <t>2640-0998</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Expense Accrual</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>1202.85</v>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>2478.43</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="28" t="inlineStr">
+        <is>
+          <t>2640-0999</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Payroll Accrual</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="D106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="28" t="inlineStr">
+        <is>
+          <t>3300-0000</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Owner Distributions</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>-102655.07</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="28" t="n"/>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="31" t="n"/>
+      <c r="D108" s="31" t="n"/>
+      <c r="E108" s="31" t="n"/>
+      <c r="F108" s="31" t="n"/>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="28" t="n"/>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="C109" s="30" t="n">
+        <v>-3824.2</v>
+      </c>
+      <c r="D109" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="30" t="n">
+        <v>-125905.68</v>
+      </c>
+      <c r="F109" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="28" t="n"/>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="31" t="n"/>
+      <c r="D110" s="31" t="n"/>
+      <c r="E110" s="31" t="n"/>
+      <c r="F110" s="31" t="n"/>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="28" t="n"/>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C111" s="30" t="n">
+        <v>4650.74</v>
+      </c>
+      <c r="D111" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="30" t="n">
+        <v>-7756.96</v>
+      </c>
+      <c r="F111" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="28" t="n"/>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="28" t="n"/>
+      <c r="B113" s="33" t="inlineStr">
+        <is>
+          <t>Period to Date</t>
+        </is>
+      </c>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="D113" s="32" t="inlineStr">
+        <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="E113" s="32" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="F113" s="28" t="n"/>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="A114" s="28" t="inlineStr">
+        <is>
+          <t>1110-4909</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>EP MSS 1st Merchants</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="28" t="n"/>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="28" t="inlineStr">
+        <is>
+          <t>1110-4925</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Storsafe of Cary Chase</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="28" t="n"/>
+    </row>
+    <row r="116" ht="15" customHeight="1">
+      <c r="A116" s="28" t="inlineStr">
+        <is>
+          <t>1110-4971</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>Storsafe Management Solutions - Cary</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="n">
+        <v>33672.76</v>
+      </c>
+      <c r="D116" s="12" t="n">
+        <v>38323.5</v>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>4650.74</v>
+      </c>
+      <c r="F116" s="28" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="28" t="n"/>
+      <c r="B117" s="33" t="inlineStr">
+        <is>
+          <t>Total Cash</t>
+        </is>
+      </c>
+      <c r="C117" s="44" t="n">
+        <v>33672.76</v>
+      </c>
+      <c r="D117" s="44" t="n">
+        <v>38323.5</v>
+      </c>
+      <c r="E117" s="44" t="n">
+        <v>4650.74</v>
+      </c>
+      <c r="F117" s="28" t="n"/>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="28" t="n"/>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="28" t="n"/>
+      <c r="B119" s="33" t="inlineStr">
+        <is>
+          <t>Year to Date</t>
+        </is>
+      </c>
+      <c r="C119" s="32" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="D119" s="32" t="inlineStr">
+        <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="E119" s="32" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="F119" s="28" t="n"/>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="28" t="inlineStr">
+        <is>
+          <t>1110-4909</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>EP MSS 1st Merchants</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="28" t="n"/>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="28" t="inlineStr">
+        <is>
+          <t>1110-4925</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Storsafe of Cary Chase</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="28" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="28" t="inlineStr">
+        <is>
+          <t>1110-4971</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>Storsafe Management Solutions - Cary</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="n">
+        <v>46080.46</v>
+      </c>
+      <c r="D122" s="12" t="n">
+        <v>38323.5</v>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>-7756.96</v>
+      </c>
+      <c r="F122" s="28" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="28" t="n"/>
+      <c r="B123" s="33" t="inlineStr">
+        <is>
+          <t>Total Cash</t>
+        </is>
+      </c>
+      <c r="C123" s="44" t="n">
+        <v>46080.46</v>
+      </c>
+      <c r="D123" s="44" t="n">
+        <v>38323.5</v>
+      </c>
+      <c r="E123" s="44" t="n">
+        <v>-7756.96</v>
+      </c>
+      <c r="F123" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>